--- a/artfynd/A 47099-2025 artfynd.xlsx
+++ b/artfynd/A 47099-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126379562</v>
+        <v>126379563</v>
       </c>
       <c r="B2" t="n">
-        <v>91263</v>
+        <v>91859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>112</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>706066</v>
+        <v>705520</v>
       </c>
       <c r="R2" t="n">
-        <v>7314076</v>
+        <v>7313969</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -744,12 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126379563</v>
+        <v>126379571</v>
       </c>
       <c r="B3" t="n">
-        <v>91195</v>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>112</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>705520</v>
+        <v>706100</v>
       </c>
       <c r="R3" t="n">
-        <v>7313969</v>
+        <v>7314054</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -850,12 +850,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -887,37 +887,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126379571</v>
+        <v>126379561</v>
       </c>
       <c r="B4" t="n">
-        <v>91241</v>
+        <v>99140</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>221952</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>706100</v>
+        <v>705903</v>
       </c>
       <c r="R4" t="n">
-        <v>7314054</v>
+        <v>7314206</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -956,12 +956,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">

--- a/artfynd/A 47099-2025 artfynd.xlsx
+++ b/artfynd/A 47099-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379563</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379571</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,8 +1005,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379561</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>